--- a/Luban/Config/Datas/#BattleMomentConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614F9193-68A5-4FA3-989E-DD086375FAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D915C1D-F8A9-4DAF-88FD-401497FB77D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11460" yWindow="2880" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="3120" yWindow="3375" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,6 +68,18 @@
   </si>
   <si>
     <t>失败ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=,),int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConditionReleation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>条件处理关系符号（0或1与）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -75,7 +87,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,6 +102,19 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -114,8 +139,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -432,92 +463,91 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="28.25" customWidth="1"/>
-    <col min="4" max="4" width="26.75" customWidth="1"/>
-    <col min="5" max="5" width="32" customWidth="1"/>
-    <col min="6" max="6" width="41.25" customWidth="1"/>
+    <col min="1" max="2" width="9" style="2"/>
+    <col min="3" max="4" width="28.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="26.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32" style="2" customWidth="1"/>
+    <col min="7" max="7" width="41.25" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>3</v>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B4" s="2">
         <v>1</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
+      <c r="E4" s="2">
+        <v>10101</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B5" s="2">
         <v>2</v>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
+      <c r="E5" s="2">
+        <v>11101</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/#BattleMomentConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D915C1D-F8A9-4DAF-88FD-401497FB77D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A18605-F3C3-4A45-B641-FAE460988620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3375" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="7200" yWindow="3990" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Luban/Config/Datas/#BattleMomentConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A18605-F3C3-4A45-B641-FAE460988620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7955169-30DD-4FF3-8583-7B3167FF03C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="3990" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="4995" yWindow="4455" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -143,11 +143,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,87 +466,87 @@
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="28.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="26.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="32" style="2" customWidth="1"/>
-    <col min="7" max="7" width="41.25" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="4" width="28.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="32" style="1" customWidth="1"/>
+    <col min="7" max="7" width="41.25" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>10101</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>2</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>11101</v>
       </c>
     </row>

--- a/Luban/Config/Datas/#BattleMomentConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7955169-30DD-4FF3-8583-7B3167FF03C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA07BEAF-D0C4-49C5-A4AD-18CDDAF15FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4995" yWindow="4455" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -80,6 +80,129 @@
   </si>
   <si>
     <t>条件处理关系符号（0或1与）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2600001,2600002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快速防守buff破防翻倍效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100003</t>
+  </si>
+  <si>
+    <t>100004</t>
+  </si>
+  <si>
+    <t>破招buff，设置为被破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>999999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3000001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>直接到当前息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置自己不可被破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1100001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700003,1200004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600001,3700001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600002,3700002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对手因招式获得的气减少100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>还原对手因招式获得的气减少100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001003</t>
+  </si>
+  <si>
+    <t>1001004</t>
+  </si>
+  <si>
+    <t>1001005</t>
+  </si>
+  <si>
+    <t>1001006</t>
+  </si>
+  <si>
+    <t>1001007</t>
+  </si>
+  <si>
+    <t>1001008</t>
+  </si>
+  <si>
+    <t>1001009</t>
+  </si>
+  <si>
+    <t>快速防守</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己随机获得一个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9999991,9999992</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -463,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -474,7 +597,7 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -494,7 +617,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -514,7 +637,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -534,20 +657,142 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1">
-        <v>10101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="E5" s="1">
-        <v>11101</v>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/#BattleMomentConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA07BEAF-D0C4-49C5-A4AD-18CDDAF15FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F176722-21C9-4BD1-81FB-DF54BD82D55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="210">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -87,14 +87,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2600001,2600002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>快速防守buff破防翻倍效果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>100001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -103,106 +95,762 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>破招buff，设置为被破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>999999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3000001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>直接到当前息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置自己不可被破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1100001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700003,1200004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600001,3700001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600002,3700002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对手因招式获得的气减少100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>还原对手因招式获得的气减少100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快速防守</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己随机获得一个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9999991,9999992</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>起势</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我获得3个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得随机键到最大值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我获得1个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>借力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1003001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1003002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破翻倍结束时清除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000201</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000202</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1003003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己获得双方招式构成相同的键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1003004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汲苦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1100002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~设置自己不可被破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1003005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破翻倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防翻倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~破翻倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~防翻倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000301</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加受击回血buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~添加受击回血buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2600003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受伤回复受伤的百分之30的血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2700003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1300001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到直接伤害回15刚气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对方伤害是否是直接伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己是否被破盾打到生命了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标前几息被调用了，是否包含当前息（1包含，0不包含）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断对方是杀式，判断是交锋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断是否互为目标</t>
+  </si>
+  <si>
+    <t>3300001</t>
+  </si>
+  <si>
+    <t>设置技能期间被打了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己行动期间被打了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果技能期间被打了，回刚气15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招架</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1005001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1005002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1005003</t>
+  </si>
+  <si>
+    <t>1005004</t>
+  </si>
+  <si>
+    <t>1005005</t>
+  </si>
+  <si>
+    <t>1005006</t>
+  </si>
+  <si>
+    <t>1005007</t>
+  </si>
+  <si>
+    <t>招式的招式的刚炁消耗转为当前50%，至多50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外炁屏障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1006001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2300001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1006002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3800001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己获取80%力的护体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1006003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回玄气10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1006004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己获取80%力的延迟护体(下个回合开始生效)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>风传</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1007001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2900002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1007002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定目标获得2层迅速,清除目标的缓速状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1007003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1007004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁+20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双方获得1个随机的键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>102002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400001,400011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>临阵之志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1008001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己加快2息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己加快1息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2900001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得一层反击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1008002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>100003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100001,100003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>100004</t>
-  </si>
-  <si>
-    <t>破招buff，设置为被破招</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>999999</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3000001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>直接到当前息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设置自己不可被破招</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1100001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>500001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>700003,1200004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3600001,3700001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3600002,3700002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对手因招式获得的气减少100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>还原对手因招式获得的气减少100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001003</t>
-  </si>
-  <si>
-    <t>1001004</t>
-  </si>
-  <si>
-    <t>1001005</t>
-  </si>
-  <si>
-    <t>1001006</t>
-  </si>
-  <si>
-    <t>1001007</t>
-  </si>
-  <si>
-    <t>1001008</t>
-  </si>
-  <si>
-    <t>1001009</t>
-  </si>
-  <si>
-    <t>快速防守</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>400001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自己随机获得一个键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9999991,9999992</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100002,100004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破防翻倍效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~破防翻倍效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1008003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在3息内反击不会低于一层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚炁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1009001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+15，玄炁+15</t>
+  </si>
+  <si>
+    <t>101001,102003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>运玄流</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1010001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2900012</t>
+  </si>
+  <si>
+    <t>自己延迟2息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1010002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1011001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1011002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁+50，每次-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+50，每次-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3810001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1012001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铩血功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1012002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1400001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己当前技能是否经过行动后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3810002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己获得等量伤害的甲</t>
+  </si>
+  <si>
+    <t>快服</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>披茧功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1014001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1014002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1014003</t>
+  </si>
+  <si>
+    <t>1014004</t>
+  </si>
+  <si>
+    <t>刚炁至少50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3900002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400006,2600102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机获得6个键，获得两层心眼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2600401,2700004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2600302</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汇力诀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1015001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1015002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1015003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得3层心眼状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得1层武增和2层力增</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2600103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2600702,2600901</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄龙灌体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1016001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1016002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1016003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1016004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>键至少5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得2层武增状态和3层力增状态和4层刚聚状态</t>
+  </si>
+  <si>
+    <t>获得5个随机的键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1500001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2600902,2600703,2600504</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3810001,102004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得100%力的血炁甲状态层数，玄气+5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1017001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1017002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得2层玄聚状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗全部的键获得（等量+4）随机的键，本回合获得1次行动次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2600602</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>600004</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -210,7 +858,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,13 +887,45 @@
       <name val="微软雅黑"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -262,7 +942,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -270,6 +950,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -586,18 +1278,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="4" width="28.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="26.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="32" style="1" customWidth="1"/>
-    <col min="7" max="7" width="41.25" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="23" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="61" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -608,16 +1303,19 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -627,17 +1325,18 @@
       <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -647,152 +1346,997 @@
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="G19" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B30" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B32" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B35" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B36" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B38" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="F38" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B39" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B43" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="1" t="s">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B45" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B47" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="1" t="s">
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B48" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B49" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B51" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B52" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B57" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B58" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B59" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B63" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F63" s="6"/>
+      <c r="G63" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B67" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B68" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B70" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B71" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B73" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B74" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="F74" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B77" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>45</v>
+      <c r="F77" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B78" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B79" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B80" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B82" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B84" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B86" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B87" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B88" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B89" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B91" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B92" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/#BattleMomentConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F176722-21C9-4BD1-81FB-DF54BD82D55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8377FF-56DD-4863-A4E8-FA01E8AF34C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="753">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -123,26 +132,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>700003,1200004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3600001,3700001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3600002,3700002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>对手因招式获得的气减少100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>还原对手因招式获得的气减少100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1001001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -163,10 +156,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>9999991,9999992</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>起势</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -223,10 +212,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1000101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>破翻倍结束时清除</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -235,26 +220,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1000102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1000201</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1000202</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1001004</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1001006</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -327,10 +296,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1000301</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>添加受击回血buff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -339,10 +304,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2600003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1000011</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -355,18 +316,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2700003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1004005</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1004006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1300001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -379,30 +332,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1000401</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到直接伤害回15刚气</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>对方伤害是否是直接伤害</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>判断自己是否被破盾打到生命了</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>目标前几息被调用了，是否包含当前息（1包含，0不包含）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>判断对方是杀式，判断是交锋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>判断是否互为目标</t>
   </si>
   <si>
@@ -440,9 +377,6 @@
     <t>1005003</t>
   </si>
   <si>
-    <t>1005004</t>
-  </si>
-  <si>
     <t>1005005</t>
   </si>
   <si>
@@ -719,22 +653,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>400006,2600102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>随机获得6个键，获得两层心眼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2600401,2700004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2600302</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>汇力诀</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -763,18 +685,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2600103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>101002</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2600702,2600901</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>玄龙灌体</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -814,10 +728,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2600902,2600703,2600504</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3810001,102004</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -846,11 +756,2200 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2600602</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>600004</t>
+    <t>600004,3400001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9999999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生生不息1018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1018001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1018002</t>
+  </si>
+  <si>
+    <t>1018003</t>
+  </si>
+  <si>
+    <t>1018004</t>
+  </si>
+  <si>
+    <t>生生不息1019</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1019001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1019002</t>
+  </si>
+  <si>
+    <t>1019003</t>
+  </si>
+  <si>
+    <t>1019004</t>
+  </si>
+  <si>
+    <t>玄炁上限+40%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁+40%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次行动不会被未带有←类留劲状态的敌手破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~本次行动不会被未带有←类留劲状态的敌手破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁上限+55%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁+55%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>104001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>104002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>102005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>102006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1020001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1020002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1020003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机获得5个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将持有键替换为不同的键各2个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁+75%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>102007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵归1020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4100002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>观</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1021001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1021002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次行动延迟1息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得3层心眼状态，本回合获得1次行动次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2900011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵归1022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1022001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1022002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1022003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁筋功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1023001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1023002</t>
+  </si>
+  <si>
+    <t>1023003</t>
+  </si>
+  <si>
+    <t>1023004</t>
+  </si>
+  <si>
+    <t>1023005</t>
+  </si>
+  <si>
+    <t>1023006</t>
+  </si>
+  <si>
+    <t>施加3层力衰状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得1个随机的键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>焚羽凌霄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1024001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1024002</t>
+  </si>
+  <si>
+    <t>1024003</t>
+  </si>
+  <si>
+    <t>获得10层缓速和10层迅速和5层玄聚和5层玄屏和5层刚聚和5层刚屏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得5层术衰状态和5层术增状态和5层技增状态和5层技衰状态和5层力衰状态和5层力增状态和5层武增状态和5层武衰状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将玄炁和刚炁的持有量变为50，获得5个随机的键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>105001,106001,400005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119000301</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19000301</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>121004102,22001100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111003101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400006,111001102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111001103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111009101,111007102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111009102,111007103,111005104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111006102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111001103,3400001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>142011103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得10层缓速和10层迅速</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得5层术衰状态和5层术增和5层技增和5层技衰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1025001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1025002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1025003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111004110,112001110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111008105,111010105,142012105,142014105</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸩姿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>补充随机的键到达持有上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本回合获得1次行动次数，下回合开始消耗全部键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1026001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1026002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3400001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900031</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移除所有的键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1027</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1027001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1027002</t>
+  </si>
+  <si>
+    <t>1027003</t>
+  </si>
+  <si>
+    <t>1027004</t>
+  </si>
+  <si>
+    <t>1027005</t>
+  </si>
+  <si>
+    <t>1027006</t>
+  </si>
+  <si>
+    <t>自己不可被武杀破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~还原自己可被武杀破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1400002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若且互为目标则消耗目标20刚炁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若与杀式交锋则刚炁+20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断对方是杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>131001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>逃之夭夭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1028001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1028002</t>
+  </si>
+  <si>
+    <t>1028003</t>
+  </si>
+  <si>
+    <t>退出战斗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9800001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>周旋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1029001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1029002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得1层回避</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得4个不同的键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111002101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遁江</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1030001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1030002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1600000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111016101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若未成为敌手的行动目标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得1层匿形状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好戏开场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1031001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1031002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次行动延迟1息</t>
+  </si>
+  <si>
+    <t>下次行动的玄炁消耗减少30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>围追堵截</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1032001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1032002</t>
+  </si>
+  <si>
+    <t>1032003</t>
+  </si>
+  <si>
+    <t>1032004</t>
+  </si>
+  <si>
+    <t>1032005</t>
+  </si>
+  <si>
+    <t>判断目标是否是杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标转来至自身</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4200021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得2层巧增</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁+40，下回合猊煞状态不会产生消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>妖化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1033001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1033002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111011102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>102008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1034001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>叩天门</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1034002</t>
+  </si>
+  <si>
+    <t>获得1层烈命状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本回合获得1次行动次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3400001,119000401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>113040101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴怒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>舔舐伤口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1036001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4300131</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清除自身3个异常状态，若清除数量不超过3个则每少1个给予1层武增1层力增1层巧增</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>垂身喘息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1037001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1037003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1037002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+100，随机获得5个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101006,400005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋失败则在下一息重复该招式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蜷缩抽搐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1038001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1038002</t>
+  </si>
+  <si>
+    <t>1038003</t>
+  </si>
+  <si>
+    <t>1038004</t>
+  </si>
+  <si>
+    <t>1038006</t>
+  </si>
+  <si>
+    <t>1038007</t>
+  </si>
+  <si>
+    <t>清除2个负面状态并获得10层避殃状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4400102,111017110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炁脉涌动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4300132</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清除自身3个异常状态，若清除数量不超过3个则每少2个给予2层武增2层力增2层巧增</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1040001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1041001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1041002</t>
+  </si>
+  <si>
+    <t>1041003</t>
+  </si>
+  <si>
+    <t>1041004</t>
+  </si>
+  <si>
+    <t>1042001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1042002</t>
+  </si>
+  <si>
+    <t>1042003</t>
+  </si>
+  <si>
+    <t>1042004</t>
+  </si>
+  <si>
+    <t>104003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>104004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁上限+40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁+40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁上限+55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁+55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>102009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生生不息1041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生生不息1042</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵归1043</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵归1044</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1043001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1043002</t>
+  </si>
+  <si>
+    <t>1043003</t>
+  </si>
+  <si>
+    <t>1044001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1044002</t>
+  </si>
+  <si>
+    <t>1044003</t>
+  </si>
+  <si>
+    <t>1046001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1047001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1047002</t>
+  </si>
+  <si>
+    <t>1047003</t>
+  </si>
+  <si>
+    <t>1047005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得1层避殃状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111017101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施加3层龙腾状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1048</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1048001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111021103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清除1个异常状态，获得5层玄聚5层刚聚和3层迅速</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1049</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1049001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4400101,111005105,111006105,111004103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1050001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1050002</t>
+  </si>
+  <si>
+    <t>1050003</t>
+  </si>
+  <si>
+    <t>1050004</t>
+  </si>
+  <si>
+    <t>1050006</t>
+  </si>
+  <si>
+    <t>1050007</t>
+  </si>
+  <si>
+    <t>2900013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己延迟3息</t>
+  </si>
+  <si>
+    <t>行动期间受到的伤害减少50%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~行动期间受到的伤害减少50%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1050008</t>
+  </si>
+  <si>
+    <t>获得3个随机的键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1051001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1051002</t>
+  </si>
+  <si>
+    <t>1051003</t>
+  </si>
+  <si>
+    <t>遮云手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+5，玄炁+5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掩护我</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1052001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1052002</t>
+  </si>
+  <si>
+    <t>将自身即将受到的敌方行动转移至目标友方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101007,102004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4210001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水戈再起</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1053001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1053002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得3层武增状态和3层力增状态，防+10，力+30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得50%力层的护体状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111009103,111007103,107001,108001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3800003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>109001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>109002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1022004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1022005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁+75%，</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若上次使用1022技能被破招</t>
+  </si>
+  <si>
+    <t>18110221</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900051</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900052</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄气消耗减少30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄气消耗增加30</t>
+  </si>
+  <si>
+    <t>110002</t>
+  </si>
+  <si>
+    <t>110001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119000502</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900061</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动次数+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1039001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1039002</t>
+  </si>
+  <si>
+    <t>1039003</t>
+  </si>
+  <si>
+    <t>1039004</t>
+  </si>
+  <si>
+    <t>119000601</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下次行动决定后获得1次行动次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4500002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据毒瘴状态层数获得增益（1：2次随机获得1层武增/术增/迅速/巧增），期间受到攻击减少2层毒瘴状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900071</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900072</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119000701</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己因招式获得的气减少100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>还原自己因招式获得的气减少100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900081</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900082</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置猊煞不会产生消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置猊煞会产生消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46900080</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46900081</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>102008,119000802</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900091</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900092</t>
+  </si>
+  <si>
+    <t>设置反击buff不会低于1层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~设置反击buff不会低于1层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>47100311</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>47100310</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119000904</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2001001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杀伐技</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2002001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2003001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>引炁为刃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汇点一破</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绝玄戮命</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2004001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2004002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2005001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2005002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2006001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2006002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式的玄炁消耗转为当前30%，至多30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式的玄炁消耗转为当前40%，至多40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式的玄炁消耗转为当前70%，至多70</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+当前30%（至少9）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+当前40%（至少12）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+当前70%（至少21）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2400001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2400002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2400003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4800001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4800002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4800003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黭幽幻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2007001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2007002</t>
+  </si>
+  <si>
+    <t>命中施加3层术式禁</t>
+  </si>
+  <si>
+    <t>盗光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2008001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2008002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得2层缓速</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若互为目标则窃取目标25%力在本回合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>112001102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贯日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2009001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2009002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗全部的键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122019103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绝技·印月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移阳秘术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挪阴秘术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卦引·天破</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卦引·尘灭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卦引·雳诛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卦引·岚萧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卦引·焚眀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卦引·泽网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卦引·岳镇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卦引·涛绝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡乱术法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得3层术衰</t>
+  </si>
+  <si>
+    <t>施加2层术衰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111007105,111008105,111009105,111010105,112011105,112012105,112013105,112014105</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>112014103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122014102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中不会造成伤害而是施加死楔状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>摒杀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敷宵剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施力压迫2024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111004110,112001110,111006105,111005105,112009105,112010105</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122009103,122010103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施加3层刚屏和3层玄屏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施力压迫2025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025002</t>
+  </si>
+  <si>
+    <t>2025003</t>
+  </si>
+  <si>
+    <t>本次行动不会被未带有↓类留劲状态的敌手破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~本次行动不会被未带有↓类留劲状态的敌手破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迭浪倾川</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026002</t>
+  </si>
+  <si>
+    <t>2026003</t>
+  </si>
+  <si>
+    <t>若持有键超过3个则随机消耗3个键在下一息重复该行动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>142014103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对交锋者施加3层术衰状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对招式目标施加1层僵硬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122015101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027002</t>
+  </si>
+  <si>
+    <t>2027003</t>
+  </si>
+  <si>
+    <t>减少目标1个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在下一息重复该行动，至多重复2次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000201</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>森森邪气2028</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2028001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机获得3个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尖啸2027</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尖啸2030</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2029001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2029002</t>
+  </si>
+  <si>
+    <t>2029003</t>
+  </si>
+  <si>
+    <t>在下一息重复该行动，至多重复3次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>森森邪气2030</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2030001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抹残香</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2031001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施加1层僵硬状态和2层破绽状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若命中时处于第一息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1900001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122015101,122007102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小雷令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2035001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2035002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施加3层技衰状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁+15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122012103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>102003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>燕子回梭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2036001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2036002</t>
+  </si>
+  <si>
+    <t>2036003</t>
+  </si>
+  <si>
+    <t>本次行动加快1息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施加1层缓速状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122001101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施加2层失持状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>截斗运</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2037001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122028102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苍涛破岳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>撕裂魂魄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2039001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁消耗转为当前40%，本次行动加快1息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2039002</t>
+  </si>
+  <si>
+    <t>2039003</t>
+  </si>
+  <si>
+    <t>2039004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2039005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中时施加5层玄屏状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若目标为鬼怪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>则造成的伤害加倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗其全部刚炁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机获得2个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2400004,2900001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>105001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122010105</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红湃华雾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2040001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+20，本回合下次术杀式威力增加15的百分比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>术杀式威力+15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>术杀式威力-15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101005,119001001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿心煞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2041001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2041002</t>
+  </si>
+  <si>
+    <t>2041003</t>
+  </si>
+  <si>
+    <t>招式的玄炁消耗转为当前60%，至多60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施加3层寒沁状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2400005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122031103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>野火</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2042001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2042002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>云螭一现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2043001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2043002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2043003</t>
+  </si>
+  <si>
+    <t>2043004</t>
+  </si>
+  <si>
+    <t>招式的玄炁消耗转为当前70%，至多70，获得2层缓速</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施加2层刚屏且造成的伤害增加50%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋施加2层刚屏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2400003,112001102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122009102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>142009103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>薄暗虹霓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2044001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>则施加1层技式禁状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若目标的刚炁低于40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122020101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月升</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2045001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2045002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁大于目标刚炁则威力增加10百分比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身玄气大于目标刚气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次行动威力+10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次行动威力-10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119001101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>净阳火</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2046001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2046002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式的玄炁消耗转为当前50%，至多50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗双方10刚炁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2400006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101012,111012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2047001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3800004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己获取30%技的护体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2048</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2048001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2048002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得3层心眼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>霜连天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2049001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施加3层玄屏状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>142010103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>残月分江</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2050001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2050002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式的玄炁消耗转为当前90%，至多90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返还消耗的键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>至少造成80%技的伤害</t>
+  </si>
+  <si>
+    <t>5300001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2400007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>追魂破</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2051001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2051002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2051003</t>
+  </si>
+  <si>
+    <t>2051004</t>
+  </si>
+  <si>
+    <t>重新在敌手中随机选择行动目标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次行动加快1息或延迟1息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施加1层过劲状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2100050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50概率成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>延迟1息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122016101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>送长离</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2052001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗目标剩余行动次数等量的键（至多2）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5400022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2053001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一次行动使用招式所需的玄炁消耗变为等量的刚炁消耗</t>
+  </si>
+  <si>
+    <t>过阴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>走旱势</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2054001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2054002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施加3层赤沸状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗目标25玄炁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122030103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2008003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>120001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>120002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>140001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>140002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>150001,160001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>150002,160002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>117000101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每有一个键该招式威力增加5的百分比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对自身造成30%技的伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50%概率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -896,7 +2995,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -921,12 +3020,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -942,7 +3035,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -961,7 +3054,13 @@
     <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1278,7 +3377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:I394"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" style="1" bestFit="1" customWidth="1"/>
@@ -1360,17 +3459,8 @@
       <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>184</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>17</v>
@@ -1378,266 +3468,245 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>49</v>
+        <v>269</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>52</v>
+        <v>270</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>53</v>
+        <v>271</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>54</v>
+        <v>272</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>75</v>
+        <v>273</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>14</v>
+        <v>274</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>89</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>36</v>
+      <c r="B13" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>31</v>
+      <c r="B14" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>453</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>22</v>
+        <v>268</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>21</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>463</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>139</v>
+        <v>747</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>142</v>
+        <v>466</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>14</v>
+        <v>464</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>19</v>
+        <v>748</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>20</v>
+        <v>467</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>14</v>
+        <v>468</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>25</v>
+        <v>472</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>27</v>
+        <v>470</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>14</v>
+        <v>469</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>26</v>
+        <v>473</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>28</v>
+        <v>471</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>475</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>32</v>
+        <v>479</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>33</v>
+        <v>477</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>60</v>
+        <v>476</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>141</v>
+        <v>480</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>143</v>
+        <v>478</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>64</v>
+        <v>643</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>745</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>66</v>
+        <v>645</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>35</v>
+      <c r="B23" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>38</v>
+        <v>683</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>743</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>39</v>
+        <v>685</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>41</v>
+        <v>684</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>744</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>42</v>
+        <v>686</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B26" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>44</v>
+      <c r="A26" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>22</v>
@@ -1648,695 +3717,3383 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
-        <v>58</v>
+        <v>45</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
-        <v>61</v>
+        <v>46</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>141</v>
+        <v>465</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
-        <v>63</v>
+      <c r="B33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B34" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B35" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>66</v>
+      <c r="A35" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>28</v>
+      <c r="A39" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="5" t="s">
-        <v>100</v>
+      <c r="B42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>139</v>
+        <v>54</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>142</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B45" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>27</v>
+      <c r="A45" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B46" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>141</v>
+        <v>243</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>64</v>
+        <v>244</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" s="5" t="s">
-        <v>109</v>
+      <c r="B50" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
-        <v>110</v>
+        <v>72</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
-        <v>112</v>
+        <v>73</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B53" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>117</v>
+      <c r="A53" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>159</v>
+        <v>22</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>119</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="5" t="s">
+      <c r="B55" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>120</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>121</v>
+        <v>85</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>122</v>
+        <v>465</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B57" s="1" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>178</v>
+        <v>28</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>124</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B62" s="1" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>179</v>
+        <v>94</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B63" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F63" s="6"/>
+        <v>96</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="G63" s="1" t="s">
-        <v>145</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A64" s="5" t="s">
-        <v>146</v>
+      <c r="B64" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B65" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>148</v>
+      <c r="A65" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A66" s="5" t="s">
-        <v>150</v>
+      <c r="B66" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B67" s="1" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>152</v>
+        <v>245</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>153</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B68" s="1" t="s">
-        <v>154</v>
+        <v>106</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A69" s="5" t="s">
-        <v>150</v>
+      <c r="B69" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B70" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>153</v>
+      <c r="A70" s="5" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B71" s="1" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>158</v>
+        <v>115</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A72" s="5" t="s">
-        <v>161</v>
+      <c r="B72" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B73" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>201</v>
+        <v>125</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>481</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>202</v>
+        <v>126</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B74" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>166</v>
+      <c r="A74" s="5" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A75" s="5" t="s">
-        <v>167</v>
+      <c r="B75" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B77" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>21</v>
+        <v>134</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B78" s="1" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>175</v>
+        <v>81</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B79" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>177</v>
+      <c r="A79" s="5" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B80" s="1" t="s">
-        <v>172</v>
+        <v>136</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A81" s="5" t="s">
-        <v>180</v>
+      <c r="B81" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B82" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>184</v>
+      <c r="A82" s="5" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B83" s="1" t="s">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B84" s="1" t="s">
-        <v>183</v>
+        <v>143</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>186</v>
+        <v>147</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>190</v>
+        <v>148</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B86" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>21</v>
+      <c r="A86" s="5" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B87" s="1" t="s">
-        <v>192</v>
+        <v>150</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>200</v>
+        <v>22</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>196</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B88" s="1" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B89" s="1" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>64</v>
+        <v>247</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>66</v>
+        <v>157</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90" s="5" t="s">
-        <v>203</v>
+      <c r="B90" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B91" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>206</v>
+      <c r="A91" s="5" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B92" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B93" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B94" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B96" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B97" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B98" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B99" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B101" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B102" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B104" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B105" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B106" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F106" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F92" s="1" t="s">
+      <c r="G106" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B107" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B109" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B110" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B111" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B112" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A113" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B114" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B115" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B116" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="G92" s="1" t="s">
-        <v>207</v>
+      <c r="F116" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A117" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B118" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B119" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A120" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B121" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B122" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B123" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B124" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B125" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A126" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B127" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B128" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B129" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B130" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B131" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B132" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B134" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B135" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B136" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B138" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B139" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B140" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B142" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B143" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B145" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B146" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B147" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B148" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B149" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B150" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A151" s="5" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B152" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B153" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B154" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155" s="5" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B156" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B157" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158" s="5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B159" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B160" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161" s="5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B162" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B163" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A164" s="5" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B165" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B166" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B167" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B168" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B169" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A170" s="5" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B171" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B172" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="F172" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A173" s="5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B174" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B175" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A176" s="5" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A178" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B179" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A180" s="5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B181" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B182" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="F182" s="5"/>
+      <c r="G182" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B183" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A184" s="5" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B185" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B186" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B187" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B188" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B189" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B190" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A191" s="5" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B192" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B193" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B194" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="G194" s="7" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B195" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A196" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B197" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A198" s="5" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B199" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B200" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B201" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="G201" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B202" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A203" s="5" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B204" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B205" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B206" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B207" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A208" s="5" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B209" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B210" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B211" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A212" s="5" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B213" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G213" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B214" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G214" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B215" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G215" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A216" s="5" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A218" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B219" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G219" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A220" s="5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B221" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="G221" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B222" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F222" s="5"/>
+      <c r="G222" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B223" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G223" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B224" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F224" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="G224" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A225" s="5" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B226" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="G226" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A227" s="5" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B228" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="F228" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="G228" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A229" s="5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B230" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F230" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G230" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B231" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="F231" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="G231" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B232" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="F232" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="G232" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B233" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="G233" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B234" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G234" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B235" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F235" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="G235" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B236" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="F236" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G236" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A237" s="5" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B238" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="F238" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G238" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B239" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="F239" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G239" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B240" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="F240" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G240" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A241" s="5" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B242" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="F242" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="G242" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B243" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="F243" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="G243" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A244" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B245" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F245" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="G245" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B246" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="F246" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="G246" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A248" s="8" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B249" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="F249" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="G249" s="1" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A250" s="8" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B251" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="F251" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="G251" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A252" s="8" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B253" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="F253" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="G253" s="1" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A254" s="8" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B255" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F255" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="G255" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B256" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="F256" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="G256" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A257" s="8" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B258" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="F258" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="G258" s="1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B259" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="F259" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="G259" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A260" s="8" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B261" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="F261" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="G261" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B262" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="F262" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="G262" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A263" s="8" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B264" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="F264" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="G264" s="6" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B265" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F265" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="G265" s="1" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A266" s="8" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B267" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="F267" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="G267" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B268" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="G268" s="8" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B269" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F269" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="G269" s="1" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A270" s="8" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B271" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="F271" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="G271" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="I271" s="6"/>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B272" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="F272" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G272" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A273" s="8" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A275" s="8" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A277" s="8" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A279" s="8" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A281" s="8" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A283" s="8" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A285" s="8" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A287" s="8" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A289" s="8" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A291" s="8" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A293" s="8" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A295" s="8" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B296" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="F296" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="G296" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B297" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="F297" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="G297" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A298" s="8" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B299" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="G299" s="1" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A300" s="8" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A302" s="8" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B303" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E303" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F303" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="G303" s="6" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B304" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="F304" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="G304" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B305" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="F305" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="G305" s="1" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A306" s="8" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B307" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="F307" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="G307" s="6" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B308" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="F308" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="G308" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B309" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F309" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="G309" s="1" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A310" s="8" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B311" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="F311" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G311" s="1" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B312" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="F312" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="G312" s="1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B313" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="G313" s="8" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A314" s="8" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B315" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="F315" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G315" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B316" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="F316" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="G316" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B317" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="G317" s="8" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A318" s="8" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B319" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="F319" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G319" s="1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A320" s="8" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B321" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="F321" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G321" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B322" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="F322" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="G322" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B323" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="G323" s="8" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A324" s="8" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B325" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="F325" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G325" s="1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A326" s="8" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B327" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="E327" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F327" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="G327" s="1" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A328" s="8" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A330" s="8" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A332" s="8" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A334" s="8" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B335" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="F335" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="G335" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B336" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="F336" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="G336" s="1" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A337" s="8" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B338" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="F338" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G338" s="1" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B339" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="F339" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="G339" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B340" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="F340" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="G340" s="1" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A341" s="8" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B342" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="F342" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="G342" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A343" s="8" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A345" s="8" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B346" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="F346" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="G346" s="1" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B347" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="C347" s="6"/>
+      <c r="D347" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="E347" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G347" s="8" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B348" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C348" s="6"/>
+      <c r="D348" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="E348" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F348" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="G348" s="1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B349" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="F349" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="G349" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B350" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="F350" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="G350" s="1" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A351" s="8" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B352" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="F352" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="G352" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A353" s="8" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B354" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="F354" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="G354" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B355" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="F355" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="G355" s="1" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B356" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="F356" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="G356" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A357" s="8" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B358" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="E358" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G358" s="8" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B359" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="F359" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="G359" s="1" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A360" s="8" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B361" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="F361" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="G361" s="1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B362" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="F362" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="G362" s="1" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B363" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="F363" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="G363" s="8" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B364" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="F364" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="G364" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A365" s="8" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B366" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="E366" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F366" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="G366" s="1" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A367" s="8" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B368" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="E368" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F368" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="G368" s="1" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B369" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="F369" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G369" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A370" s="8" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B371" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="F371" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="G371" s="1" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B372" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D372" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E372" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F372" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="G372" s="1" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A373" s="8" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B374" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="F374" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="G374" s="1" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A375" s="8" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B376" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="F376" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G376" s="1" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B377" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="F377" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="G377" s="1" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A378" s="8" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B379" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="F379" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="G379" s="1" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A380" s="8" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B381" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="F381" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="G381" s="1" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B382" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="C382" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="D382" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="E382" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F382" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="G382" s="1" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A383" s="8" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B384" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="G384" s="8" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B385" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="C385" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="D385" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="E385" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F385" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G385" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="H385" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="I385" s="1" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B386" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F386" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="G386" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B387" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="F387" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="G387" s="1" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A388" s="8" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B389" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="F389" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="G389" s="1" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A390" s="8" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B391" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="G391" s="8" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A392" s="8" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B393" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="F393" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="G393" s="1" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B394" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="F394" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="G394" s="1" t="s">
+        <v>739</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/#BattleMomentConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8377FF-56DD-4863-A4E8-FA01E8AF34C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCAF87B-E4E0-4631-893A-34851935840D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>

--- a/Luban/Config/Datas/#BattleMomentConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561D8A67-746F-4D67-95E7-49BED5B9B56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D847B584-5757-44ED-978C-CDEE38AC7D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>

--- a/Luban/Config/Datas/#BattleMomentConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D847B584-5757-44ED-978C-CDEE38AC7D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34337EAD-CF09-4F18-9027-B382907084C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6638,7 +6638,7 @@
     <col min="1" max="1" width="17.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
     <col min="3" max="3" width="11" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="1" customWidth="1"/>
+    <col min="4" max="4" width="39.125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="27.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="46.125" style="1" customWidth="1"/>
